--- a/uipath_hackathon/Docs/acme-call-center-analytics-tasks.xlsx
+++ b/uipath_hackathon/Docs/acme-call-center-analytics-tasks.xlsx
@@ -745,7 +745,7 @@
       <c r="I2" s="4" t="inlineStr"/>
       <c r="J2" s="4" t="inlineStr">
         <is>
-          <t>Not Started</t>
+          <t>Done</t>
         </is>
       </c>
       <c r="K2" s="4" t="inlineStr">
